--- a/surgical_staging/STAGED_CRS620MI_Supplier_Addresses.xlsx
+++ b/surgical_staging/STAGED_CRS620MI_Supplier_Addresses.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="158">
   <si>
     <t>SACONO</t>
   </si>
@@ -88,25 +88,37 @@
     <t>100.0</t>
   </si>
   <si>
-    <t xml:space="preserve">160118    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">160231    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">500970    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">501013    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">501023    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">395056    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">395453    </t>
+    <t xml:space="preserve">502125    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">166993    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">160047    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">167602    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169833    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169912    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169920    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">169944    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">170580    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">170590    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">170592    </t>
   </si>
   <si>
     <t>1.0</t>
@@ -115,286 +127,367 @@
     <t>10.0</t>
   </si>
   <si>
+    <t xml:space="preserve">1     </t>
+  </si>
+  <si>
     <t xml:space="preserve">01    </t>
   </si>
   <si>
-    <t xml:space="preserve">1     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">10    </t>
+    <t>20051101.0</t>
+  </si>
+  <si>
+    <t>20061122.0</t>
   </si>
   <si>
     <t>19990628.0</t>
   </si>
   <si>
-    <t>20000324.0</t>
-  </si>
-  <si>
-    <t>20000901.0</t>
-  </si>
-  <si>
-    <t>20121029.0</t>
-  </si>
-  <si>
-    <t>20190312.0</t>
-  </si>
-  <si>
-    <t>20230814.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampacet Canada                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berg Industrial Service             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soarus, L.L.C.                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stonhard                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun Chemical Corp                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULINE SHIPPING SUPPLIES SDERLDECV   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flex Films (USA), Inc.              </t>
+    <t>20140515.0</t>
+  </si>
+  <si>
+    <t>20210527.0</t>
+  </si>
+  <si>
+    <t>20230227.0</t>
+  </si>
+  <si>
+    <t>20230424.0</t>
+  </si>
+  <si>
+    <t>20230811.0</t>
+  </si>
+  <si>
+    <t>20251003.0</t>
+  </si>
+  <si>
+    <t>20251210.0</t>
+  </si>
+  <si>
+    <t>20251219.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenia Polymers                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equistar Chemicals LP               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chevron Phillips                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chevron Phillips Chemical Co        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fernando Marquez                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formosa Plastics Corporation, Texas </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PureCycle Ohio, LLC                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Westlake Polymers Inc               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG Chem America, Inc                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinnacle Polymers LLC               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilk 2 Sp. z o. o                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xiamen Deguan Technology Co. Ltd.   </t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t xml:space="preserve">101 Sasaga Drive                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">P.O. Box 15009, Station A           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">6355 Shawson Dr.                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3930 Ventura Drive, Suite 300       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">c/o PO Box 931947                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO Box 2193                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">AVE AGUILA REAL #19533              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1221 North Black Branch Road        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PO Box 857504                       </t>
+    <t xml:space="preserve">PO Box 123074, Dept. 3074           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1221 McKinney                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Box 4910                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Box 847885                       </t>
   </si>
   <si>
     <t xml:space="preserve">                                    </t>
   </si>
   <si>
-    <t xml:space="preserve">TD BANK TOWER                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit #1                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arlington Heights, IL  60004        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carol Stream, IL  60132-2193        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARQUE INDUSTRIAL BAJA MAQ          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elizabethtown KY 42701              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minneapolis, MN  55485-7504         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">66 WELLINGTON ST W. SUITE 4500      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MISSISSAUGA, ON                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cleveland, OH   44193               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIJUANA, BC, MEXICO                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitchener, ON                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toronto, ON   M5W 1C1               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">L5T 1S7                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">USS000718PA0                        </t>
+    <t xml:space="preserve">201 Formosa Drive                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 Peach Tree Hill Road              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">925 County Road 1A                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2801 Post Oak Blvd                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Box 100785                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3475 Piedmont Rd NE                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">One Pinnacle Ave                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ul. Hutnicza 31, 22-100 Che?m       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ul. Bramowa 2-8, 20-111 Lublin      </t>
+  </si>
+  <si>
+    <t>1/F No. 7 Anbian Road, Torch Hi-Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas, TX  75312-3074              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suite 1600                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suite 700                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Woodlands, TX 77387-4910        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas, TX  75284-7885              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point Comfort, TX 77978             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Livingston, NJ 07039                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bld 560                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suite 600                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atlanta, GA, 30384                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suite 1200                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garyville, LA 70051                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial Zone (Xiangan) Xiamen    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston TX 77010                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston, TX 77010                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attn: K-Resin Customer Service      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ironton, OH 45638                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston TX, 77056                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atlanta, GA 30305                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">China                               </t>
   </si>
   <si>
     <t xml:space="preserve">US </t>
   </si>
   <si>
-    <t xml:space="preserve">CA </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MX </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N2C2G8    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">M5W 1C1   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">L5T 1S7   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">60004     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">44193     </t>
-  </si>
-  <si>
-    <t>60132-2193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22505     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">42701     </t>
-  </si>
-  <si>
-    <t>55485-7504</t>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN </t>
+  </si>
+  <si>
+    <t>75312-3074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77010     </t>
+  </si>
+  <si>
+    <t>77216-4029</t>
+  </si>
+  <si>
+    <t>77387-4910</t>
+  </si>
+  <si>
+    <t>75284-0598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">77978     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">07039     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">45638     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">77056     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30386     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30305     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">70051     </t>
   </si>
   <si>
     <t xml:space="preserve">      </t>
   </si>
   <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
     <t>000</t>
   </si>
   <si>
-    <t>XX</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>IL</t>
+    <t>TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>NJ</t>
   </si>
   <si>
     <t>OH</t>
   </si>
   <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t>MN</t>
-  </si>
-  <si>
-    <t>20191127.0</t>
-  </si>
-  <si>
-    <t>20001121.0</t>
-  </si>
-  <si>
-    <t>115329.0</t>
-  </si>
-  <si>
-    <t>92936.0</t>
-  </si>
-  <si>
-    <t>141519.0</t>
-  </si>
-  <si>
-    <t>141523.0</t>
-  </si>
-  <si>
-    <t>141524.0</t>
-  </si>
-  <si>
-    <t>163809.0</t>
-  </si>
-  <si>
-    <t>211148.0</t>
-  </si>
-  <si>
-    <t>100538.0</t>
-  </si>
-  <si>
-    <t>20131104.0</t>
-  </si>
-  <si>
-    <t>20180924.0</t>
-  </si>
-  <si>
-    <t>20250219.0</t>
-  </si>
-  <si>
-    <t>20050127.0</t>
-  </si>
-  <si>
-    <t>20251204.0</t>
-  </si>
-  <si>
-    <t>20130604.0</t>
-  </si>
-  <si>
-    <t>9.0</t>
-  </si>
-  <si>
-    <t>15.0</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>20.0</t>
-  </si>
-  <si>
-    <t>4.0</t>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>20051206.0</t>
+  </si>
+  <si>
+    <t>20071011.0</t>
+  </si>
+  <si>
+    <t>20080729.0</t>
+  </si>
+  <si>
+    <t>163202.0</t>
+  </si>
+  <si>
+    <t>123850.0</t>
+  </si>
+  <si>
+    <t>104230.0</t>
+  </si>
+  <si>
+    <t>165712.0</t>
+  </si>
+  <si>
+    <t>170011.0</t>
+  </si>
+  <si>
+    <t>152444.0</t>
+  </si>
+  <si>
+    <t>142248.0</t>
+  </si>
+  <si>
+    <t>142308.0</t>
+  </si>
+  <si>
+    <t>95108.0</t>
+  </si>
+  <si>
+    <t>163304.0</t>
+  </si>
+  <si>
+    <t>163328.0</t>
+  </si>
+  <si>
+    <t>85047.0</t>
+  </si>
+  <si>
+    <t>131809.0</t>
+  </si>
+  <si>
+    <t>92116.0</t>
+  </si>
+  <si>
+    <t>92132.0</t>
+  </si>
+  <si>
+    <t>90642.0</t>
+  </si>
+  <si>
+    <t>90713.0</t>
+  </si>
+  <si>
+    <t>20211004.0</t>
+  </si>
+  <si>
+    <t>20081203.0</t>
+  </si>
+  <si>
+    <t>20120809.0</t>
+  </si>
+  <si>
+    <t>20101104.0</t>
+  </si>
+  <si>
+    <t>20081027.0</t>
   </si>
   <si>
     <t>16.0</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">W45METYD  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W45ACBEH  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W45MEVNH  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W20ACCAE  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W20ACSNE  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W70MEFOR  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W70MEMSM  </t>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>39.0</t>
+  </si>
+  <si>
+    <t>32.0</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20PUNEW  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W35ACMNG  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W40MEMEJ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W35ACNYD  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W41MEMLB  </t>
   </si>
 </sst>
 </file>
@@ -752,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -834,67 +927,67 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="J2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="L2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="M2" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="N2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="R2" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="S2" t="s">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="T2" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="U2" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="V2" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="W2" t="s">
-        <v>120</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -902,70 +995,70 @@
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="J3" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="K3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="L3" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="M3" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="N3" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P3" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="R3" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="S3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="U3" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="V3" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="W3" t="s">
-        <v>121</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -976,67 +1069,67 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H4" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="J4" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L4" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P4" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q4" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="R4" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="S4" t="s">
-        <v>37</v>
+        <v>124</v>
       </c>
       <c r="T4" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="U4" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="V4" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="W4" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1044,70 +1137,70 @@
         <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H5" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J5" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="L5" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="M5" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O5" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P5" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="R5" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="S5" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="T5" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="U5" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="V5" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="W5" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1118,67 +1211,67 @@
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L6" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="M6" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O6" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P6" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q6" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="R6" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="S6" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="T6" t="s">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="U6" t="s">
-        <v>41</v>
+        <v>147</v>
       </c>
       <c r="V6" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="W6" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1189,67 +1282,67 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L7" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="M7" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="N7" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P7" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="R7" t="s">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="S7" t="s">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="T7" t="s">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="U7" t="s">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="V7" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="W7" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1260,67 +1353,67 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I8" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L8" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s">
-        <v>83</v>
+        <v>108</v>
       </c>
       <c r="N8" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q8" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="R8" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="S8" t="s">
-        <v>97</v>
+        <v>43</v>
       </c>
       <c r="T8" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="V8" t="s">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="W8" t="s">
-        <v>123</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -1328,70 +1421,70 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I9" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="J9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K9" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="L9" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="M9" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="N9" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O9" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P9" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q9" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="R9" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="S9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="T9" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
       <c r="U9" t="s">
-        <v>111</v>
+        <v>43</v>
       </c>
       <c r="V9" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="W9" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1399,70 +1492,70 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I10" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="K10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="L10" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="M10" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="N10" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="O10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="P10" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="R10" t="s">
-        <v>94</v>
+        <v>120</v>
       </c>
       <c r="S10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="T10" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="U10" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="V10" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="W10" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1470,70 +1563,567 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" t="s">
+        <v>95</v>
+      </c>
+      <c r="K11" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" t="s">
+        <v>98</v>
+      </c>
+      <c r="M11" t="s">
+        <v>111</v>
+      </c>
+      <c r="N11" t="s">
+        <v>115</v>
+      </c>
+      <c r="O11" t="s">
+        <v>99</v>
+      </c>
+      <c r="P11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>99</v>
+      </c>
+      <c r="R11" t="s">
+        <v>117</v>
+      </c>
+      <c r="S11" t="s">
+        <v>45</v>
+      </c>
+      <c r="T11" t="s">
+        <v>135</v>
+      </c>
+      <c r="U11" t="s">
+        <v>45</v>
+      </c>
+      <c r="V11" t="s">
+        <v>35</v>
+      </c>
+      <c r="W11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" t="s">
+        <v>67</v>
+      </c>
+      <c r="L12" t="s">
+        <v>98</v>
+      </c>
+      <c r="M12" t="s">
+        <v>112</v>
+      </c>
+      <c r="N12" t="s">
+        <v>115</v>
+      </c>
+      <c r="O12" t="s">
+        <v>99</v>
+      </c>
+      <c r="P12" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>99</v>
+      </c>
+      <c r="R12" t="s">
+        <v>121</v>
+      </c>
+      <c r="S12" t="s">
+        <v>45</v>
+      </c>
+      <c r="T12" t="s">
+        <v>136</v>
+      </c>
+      <c r="U12" t="s">
+        <v>45</v>
+      </c>
+      <c r="V12" t="s">
+        <v>152</v>
+      </c>
+      <c r="W12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
         <v>31</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C13" t="s">
         <v>35</v>
       </c>
-      <c r="E11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I13" t="s">
+        <v>88</v>
+      </c>
+      <c r="J13" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" t="s">
+        <v>67</v>
+      </c>
+      <c r="L13" t="s">
+        <v>98</v>
+      </c>
+      <c r="M13" t="s">
+        <v>113</v>
+      </c>
+      <c r="N13" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13" t="s">
+        <v>99</v>
+      </c>
+      <c r="P13" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>99</v>
+      </c>
+      <c r="R13" t="s">
+        <v>121</v>
+      </c>
+      <c r="S13" t="s">
+        <v>46</v>
+      </c>
+      <c r="T13" t="s">
+        <v>137</v>
+      </c>
+      <c r="U13" t="s">
+        <v>46</v>
+      </c>
+      <c r="V13" t="s">
+        <v>35</v>
+      </c>
+      <c r="W13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" t="s">
+        <v>114</v>
+      </c>
+      <c r="N14" t="s">
+        <v>115</v>
+      </c>
+      <c r="O14" t="s">
+        <v>99</v>
+      </c>
+      <c r="P14" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>99</v>
+      </c>
+      <c r="R14" t="s">
+        <v>122</v>
+      </c>
+      <c r="S14" t="s">
+        <v>47</v>
+      </c>
+      <c r="T14" t="s">
+        <v>138</v>
+      </c>
+      <c r="U14" t="s">
+        <v>47</v>
+      </c>
+      <c r="V14" t="s">
+        <v>35</v>
+      </c>
+      <c r="W14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" t="s">
+        <v>62</v>
+      </c>
+      <c r="H15" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" t="s">
+        <v>67</v>
+      </c>
+      <c r="J15" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" t="s">
+        <v>67</v>
+      </c>
+      <c r="L15" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" t="s">
+        <v>107</v>
+      </c>
+      <c r="N15" t="s">
+        <v>115</v>
+      </c>
+      <c r="O15" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>99</v>
+      </c>
+      <c r="R15" t="s">
+        <v>118</v>
+      </c>
+      <c r="S15" t="s">
+        <v>48</v>
+      </c>
+      <c r="T15" t="s">
+        <v>139</v>
+      </c>
+      <c r="U15" t="s">
+        <v>48</v>
+      </c>
+      <c r="V15" t="s">
+        <v>152</v>
+      </c>
+      <c r="W15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" t="s">
+        <v>76</v>
+      </c>
+      <c r="I16" t="s">
+        <v>67</v>
+      </c>
+      <c r="J16" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" t="s">
+        <v>67</v>
+      </c>
+      <c r="L16" t="s">
+        <v>100</v>
+      </c>
+      <c r="M16" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" t="s">
+        <v>115</v>
+      </c>
+      <c r="O16" t="s">
+        <v>99</v>
+      </c>
+      <c r="P16" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>99</v>
+      </c>
+      <c r="R16" t="s">
+        <v>118</v>
+      </c>
+      <c r="S16" t="s">
+        <v>48</v>
+      </c>
+      <c r="T16" t="s">
+        <v>140</v>
+      </c>
+      <c r="U16" t="s">
+        <v>48</v>
+      </c>
+      <c r="V16" t="s">
+        <v>152</v>
+      </c>
+      <c r="W16" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" t="s">
         <v>49</v>
       </c>
-      <c r="H11" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J11" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" t="s">
-        <v>75</v>
-      </c>
-      <c r="M11" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" t="s">
-        <v>87</v>
-      </c>
-      <c r="O11" t="s">
-        <v>88</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="F17" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" t="s">
+        <v>90</v>
+      </c>
+      <c r="J17" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" t="s">
+        <v>101</v>
+      </c>
+      <c r="M17" t="s">
+        <v>107</v>
+      </c>
+      <c r="N17" t="s">
+        <v>115</v>
+      </c>
+      <c r="O17" t="s">
+        <v>99</v>
+      </c>
+      <c r="P17" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>99</v>
+      </c>
+      <c r="R17" t="s">
+        <v>118</v>
+      </c>
+      <c r="S17" t="s">
         <v>49</v>
       </c>
-      <c r="Q11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R11" t="s">
-        <v>95</v>
-      </c>
-      <c r="S11" t="s">
-        <v>41</v>
-      </c>
-      <c r="T11" t="s">
-        <v>105</v>
-      </c>
-      <c r="U11" t="s">
-        <v>41</v>
-      </c>
-      <c r="V11" t="s">
-        <v>119</v>
-      </c>
-      <c r="W11" t="s">
-        <v>123</v>
+      <c r="T17" t="s">
+        <v>141</v>
+      </c>
+      <c r="U17" t="s">
+        <v>49</v>
+      </c>
+      <c r="V17" t="s">
+        <v>35</v>
+      </c>
+      <c r="W17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I18" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>67</v>
+      </c>
+      <c r="K18" t="s">
+        <v>97</v>
+      </c>
+      <c r="L18" t="s">
+        <v>101</v>
+      </c>
+      <c r="M18" t="s">
+        <v>107</v>
+      </c>
+      <c r="N18" t="s">
+        <v>115</v>
+      </c>
+      <c r="O18" t="s">
+        <v>99</v>
+      </c>
+      <c r="P18" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>99</v>
+      </c>
+      <c r="R18" t="s">
+        <v>118</v>
+      </c>
+      <c r="S18" t="s">
+        <v>49</v>
+      </c>
+      <c r="T18" t="s">
+        <v>142</v>
+      </c>
+      <c r="U18" t="s">
+        <v>49</v>
+      </c>
+      <c r="V18" t="s">
+        <v>152</v>
+      </c>
+      <c r="W18" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/surgical_staging/STAGED_CRS620MI_Supplier_Addresses.xlsx
+++ b/surgical_staging/STAGED_CRS620MI_Supplier_Addresses.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="229">
   <si>
     <t>SACONO</t>
   </si>
@@ -88,9 +88,36 @@
     <t>100.0</t>
   </si>
   <si>
+    <t xml:space="preserve">500003    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">376047    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">136036    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">140376    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">502125    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">137652    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">379811    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">379886    </t>
+  </si>
+  <si>
     <t xml:space="preserve">159392    </t>
   </si>
   <si>
+    <t>2.0</t>
+  </si>
+  <si>
     <t>1.0</t>
   </si>
   <si>
@@ -100,9 +127,87 @@
     <t xml:space="preserve">1     </t>
   </si>
   <si>
+    <t xml:space="preserve">2     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3     </t>
+  </si>
+  <si>
+    <t>20000912.0</t>
+  </si>
+  <si>
+    <t>20011130.0</t>
+  </si>
+  <si>
+    <t>20021101.0</t>
+  </si>
+  <si>
+    <t>20050505.0</t>
+  </si>
+  <si>
+    <t>20051101.0</t>
+  </si>
+  <si>
+    <t>20070716.0</t>
+  </si>
+  <si>
+    <t>20081001.0</t>
+  </si>
+  <si>
+    <t>20120905.0</t>
+  </si>
+  <si>
+    <t>20160620.0</t>
+  </si>
+  <si>
+    <t>20160926.0</t>
+  </si>
+  <si>
+    <t>20170403.0</t>
+  </si>
+  <si>
+    <t>20171011.0</t>
+  </si>
+  <si>
+    <t>20190408.0</t>
+  </si>
+  <si>
+    <t>20191029.0</t>
+  </si>
+  <si>
+    <t>20200309.0</t>
+  </si>
+  <si>
     <t>20201130.0</t>
   </si>
   <si>
+    <t>20230810.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampacet Corporation                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dow Chemical Company                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dow Chemical Canada ULC             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soarus L.L.C.                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenia Polymers                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dow Chemical Canada                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Trade Solutions       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SK Primacor Americas LLC            </t>
+  </si>
+  <si>
     <t xml:space="preserve">National Research Council Canada    </t>
   </si>
   <si>
@@ -112,58 +217,490 @@
     <t>0.0</t>
   </si>
   <si>
+    <t xml:space="preserve">125 Ampacet Drive                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24426 Network Place                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2040 Dow Center                     </t>
+  </si>
+  <si>
+    <t>C/O CIBC Lock Box Dept 2Nd Fl 301-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.O. 94018                          </t>
+  </si>
+  <si>
+    <t>Customer Service Center 2040 Dow Cen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3930 Ventura Drive Suite 355        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LockBox B3911                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Box 123074, Dept. 3074           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock Box B2908                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">fka Holje Customs Broker            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">#2400 215-2nd street S.W.           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPT CH 16682                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">P.O. Box 12607                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3930 Ventura Drive , Suite 300      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11700 Katy Freeway Suite 900        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">75 Remittance Drive                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lockbox 911061 P.O. Box 4090        </t>
+  </si>
+  <si>
     <t xml:space="preserve">Finance Branch                      </t>
   </si>
   <si>
+    <t xml:space="preserve">PO Box 857504                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeRidder, LA 70634                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicago, IL 60673-1244              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midland, Michigan 48674             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calgary, AB                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicago , IL                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midland, MI                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arlington Heights, IL               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Box 6986 Station D               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dallas, TX  75312-3074              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C.P. 11595, Succ. Centre Ville      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PO Box 125                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">P O Box 125                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calgary AB T2P 1M4                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palatine, IL  60055-6682            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Forks, ND  58208-2607         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arlington Heights, IL 60004         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palatine, IL 60055-6682             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston TX 77079                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dept 6913                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dept. 6913                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STN A Toronto ON                    </t>
+  </si>
+  <si>
     <t xml:space="preserve">                                    </t>
   </si>
   <si>
+    <t xml:space="preserve">Minneapolis, MN 55485-7504          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S.A.                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montréal, QC    H3C 5N7             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plentywood MT  59254                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plentywood MT 59254                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicago, IL  60675-6913             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicago IL 60675-6913               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5W 0E9                             </t>
+  </si>
+  <si>
     <t xml:space="preserve">Ottawa, ON  K1A 0R6                 </t>
   </si>
   <si>
     <t xml:space="preserve">1200 Montreal Road, Building M-58   </t>
   </si>
   <si>
-    <t xml:space="preserve">Canada                              </t>
+    <t xml:space="preserve">afrisbie4@dow.com                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2R 0C7                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60690                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">48640                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2P 5A4                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">talbelo@soarus.com                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cscard@sk.com                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US </t>
   </si>
   <si>
     <t xml:space="preserve">CA </t>
   </si>
   <si>
+    <t xml:space="preserve">70634     </t>
+  </si>
+  <si>
+    <t>60673-1244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48674     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2R 0C7   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60690     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">48640     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60004     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2P 5A4   </t>
+  </si>
+  <si>
+    <t>75312-3074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3C 5N7   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">59254     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2P 1M4   </t>
+  </si>
+  <si>
+    <t>60055-6682</t>
+  </si>
+  <si>
+    <t>58208-2607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77079     </t>
+  </si>
+  <si>
+    <t>60675-5913</t>
+  </si>
+  <si>
+    <t>60675-6913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M5W 0E9   </t>
+  </si>
+  <si>
     <t xml:space="preserve">K1A 0R6   </t>
   </si>
   <si>
+    <t>55485-7504</t>
+  </si>
+  <si>
     <t xml:space="preserve">      </t>
   </si>
   <si>
     <t xml:space="preserve">   </t>
   </si>
   <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>AB</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>QC</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
     <t>ON</t>
   </si>
   <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>20001214.0</t>
+  </si>
+  <si>
+    <t>20011217.0</t>
+  </si>
+  <si>
+    <t>20021121.0</t>
+  </si>
+  <si>
+    <t>20050609.0</t>
+  </si>
+  <si>
+    <t>20051206.0</t>
+  </si>
+  <si>
+    <t>20070717.0</t>
+  </si>
+  <si>
+    <t>20081106.0</t>
+  </si>
+  <si>
+    <t>20160622.0</t>
+  </si>
+  <si>
+    <t>20160927.0</t>
+  </si>
+  <si>
+    <t>20170404.0</t>
+  </si>
+  <si>
+    <t>20171012.0</t>
+  </si>
+  <si>
+    <t>20190410.0</t>
+  </si>
+  <si>
     <t>20201203.0</t>
   </si>
   <si>
+    <t>95819.0</t>
+  </si>
+  <si>
+    <t>132403.0</t>
+  </si>
+  <si>
+    <t>103106.0</t>
+  </si>
+  <si>
+    <t>184904.0</t>
+  </si>
+  <si>
+    <t>132815.0</t>
+  </si>
+  <si>
+    <t>163202.0</t>
+  </si>
+  <si>
+    <t>122432.0</t>
+  </si>
+  <si>
+    <t>112420.0</t>
+  </si>
+  <si>
+    <t>112512.0</t>
+  </si>
+  <si>
+    <t>134036.0</t>
+  </si>
+  <si>
+    <t>124931.0</t>
+  </si>
+  <si>
+    <t>155214.0</t>
+  </si>
+  <si>
+    <t>115623.0</t>
+  </si>
+  <si>
+    <t>115723.0</t>
+  </si>
+  <si>
+    <t>144011.0</t>
+  </si>
+  <si>
+    <t>151527.0</t>
+  </si>
+  <si>
+    <t>102901.0</t>
+  </si>
+  <si>
+    <t>103304.0</t>
+  </si>
+  <si>
     <t>93758.0</t>
   </si>
   <si>
     <t>95201.0</t>
   </si>
   <si>
+    <t>134233.0</t>
+  </si>
+  <si>
+    <t>20180720.0</t>
+  </si>
+  <si>
+    <t>20240514.0</t>
+  </si>
+  <si>
+    <t>20210511.0</t>
+  </si>
+  <si>
+    <t>20140611.0</t>
+  </si>
+  <si>
+    <t>20211004.0</t>
+  </si>
+  <si>
+    <t>20180417.0</t>
+  </si>
+  <si>
+    <t>20250428.0</t>
+  </si>
+  <si>
+    <t>20240606.0</t>
+  </si>
+  <si>
+    <t>20190415.0</t>
+  </si>
+  <si>
     <t>20260331.0</t>
   </si>
   <si>
+    <t>30.0</t>
+  </si>
+  <si>
+    <t>33.0</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>9.0</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>5.0</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
     <t>3.0</t>
   </si>
   <si>
-    <t>2.0</t>
+    <t>15.0</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20PUROC  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25ADTRJ  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15ACJRW  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W15PUDAH  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W20PUNEW  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25MEING  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">W25PUKES  </t>
   </si>
   <si>
     <t xml:space="preserve">W15ACRAF  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">W15ACJRW  </t>
   </si>
 </sst>
 </file>
@@ -521,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -603,67 +1140,67 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="N2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O2" t="s">
+        <v>153</v>
+      </c>
+      <c r="P2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>153</v>
+      </c>
+      <c r="R2" t="s">
+        <v>154</v>
+      </c>
+      <c r="S2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>40</v>
-      </c>
-      <c r="R2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
       <c r="T2" t="s">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="U2" t="s">
-        <v>45</v>
+        <v>198</v>
       </c>
       <c r="V2" t="s">
-        <v>46</v>
+        <v>208</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -674,67 +1211,1629 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K3" t="s">
+        <v>108</v>
+      </c>
+      <c r="L3" t="s">
+        <v>130</v>
+      </c>
+      <c r="M3" t="s">
+        <v>133</v>
+      </c>
+      <c r="N3" t="s">
+        <v>152</v>
+      </c>
+      <c r="O3" t="s">
+        <v>153</v>
+      </c>
+      <c r="P3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>153</v>
+      </c>
+      <c r="R3" t="s">
+        <v>155</v>
+      </c>
+      <c r="S3" t="s">
+        <v>164</v>
+      </c>
+      <c r="T3" t="s">
+        <v>178</v>
+      </c>
+      <c r="U3" t="s">
+        <v>198</v>
+      </c>
+      <c r="V3" t="s">
+        <v>209</v>
+      </c>
+      <c r="W3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K4" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" t="s">
+        <v>130</v>
+      </c>
+      <c r="M4" t="s">
+        <v>134</v>
+      </c>
+      <c r="N4" t="s">
+        <v>152</v>
+      </c>
+      <c r="O4" t="s">
+        <v>153</v>
+      </c>
+      <c r="P4" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>153</v>
+      </c>
+      <c r="R4" t="s">
+        <v>156</v>
+      </c>
+      <c r="S4" t="s">
+        <v>165</v>
+      </c>
+      <c r="T4" t="s">
+        <v>179</v>
+      </c>
+      <c r="U4" t="s">
+        <v>199</v>
+      </c>
+      <c r="V4" t="s">
+        <v>210</v>
+      </c>
+      <c r="W4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J5" t="s">
+        <v>111</v>
+      </c>
+      <c r="K5" t="s">
+        <v>122</v>
+      </c>
+      <c r="L5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M5" t="s">
+        <v>135</v>
+      </c>
+      <c r="N5" t="s">
+        <v>152</v>
+      </c>
+      <c r="O5" t="s">
+        <v>153</v>
+      </c>
+      <c r="P5" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>153</v>
+      </c>
+      <c r="R5" t="s">
+        <v>157</v>
+      </c>
+      <c r="S5" t="s">
+        <v>166</v>
+      </c>
+      <c r="T5" t="s">
+        <v>180</v>
+      </c>
+      <c r="U5" t="s">
+        <v>200</v>
+      </c>
+      <c r="V5" t="s">
+        <v>211</v>
+      </c>
+      <c r="W5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" t="s">
+        <v>91</v>
+      </c>
+      <c r="J6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N6" t="s">
+        <v>152</v>
+      </c>
+      <c r="O6" t="s">
+        <v>153</v>
+      </c>
+      <c r="P6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>153</v>
+      </c>
+      <c r="R6" t="s">
+        <v>155</v>
+      </c>
+      <c r="S6" t="s">
+        <v>166</v>
+      </c>
+      <c r="T6" t="s">
+        <v>180</v>
+      </c>
+      <c r="U6" t="s">
+        <v>201</v>
+      </c>
+      <c r="V6" t="s">
+        <v>212</v>
+      </c>
+      <c r="W6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L7" t="s">
+        <v>130</v>
+      </c>
+      <c r="M7" t="s">
+        <v>137</v>
+      </c>
+      <c r="N7" t="s">
+        <v>152</v>
+      </c>
+      <c r="O7" t="s">
+        <v>153</v>
+      </c>
+      <c r="P7" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>153</v>
+      </c>
+      <c r="R7" t="s">
+        <v>156</v>
+      </c>
+      <c r="S7" t="s">
+        <v>166</v>
+      </c>
+      <c r="T7" t="s">
+        <v>180</v>
+      </c>
+      <c r="U7" t="s">
+        <v>200</v>
+      </c>
+      <c r="V7" t="s">
+        <v>213</v>
+      </c>
+      <c r="W7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K8" t="s">
+        <v>125</v>
+      </c>
+      <c r="L8" t="s">
+        <v>130</v>
+      </c>
+      <c r="M8" t="s">
+        <v>138</v>
+      </c>
+      <c r="N8" t="s">
+        <v>152</v>
+      </c>
+      <c r="O8" t="s">
+        <v>153</v>
+      </c>
+      <c r="P8" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>153</v>
+      </c>
+      <c r="R8" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" t="s">
+        <v>166</v>
+      </c>
+      <c r="T8" t="s">
+        <v>180</v>
+      </c>
+      <c r="U8" t="s">
+        <v>201</v>
+      </c>
+      <c r="V8" t="s">
+        <v>214</v>
+      </c>
+      <c r="W8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J9" t="s">
+        <v>90</v>
+      </c>
+      <c r="K9" t="s">
+        <v>126</v>
+      </c>
+      <c r="L9" t="s">
+        <v>131</v>
+      </c>
+      <c r="M9" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" t="s">
+        <v>152</v>
+      </c>
+      <c r="O9" t="s">
+        <v>153</v>
+      </c>
+      <c r="P9" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>153</v>
+      </c>
+      <c r="R9" t="s">
+        <v>157</v>
+      </c>
+      <c r="S9" t="s">
+        <v>167</v>
+      </c>
+      <c r="T9" t="s">
+        <v>181</v>
+      </c>
+      <c r="U9" t="s">
+        <v>200</v>
+      </c>
+      <c r="V9" t="s">
+        <v>35</v>
+      </c>
+      <c r="W9" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J10" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>108</v>
+      </c>
+      <c r="L10" t="s">
+        <v>130</v>
+      </c>
+      <c r="M10" t="s">
+        <v>140</v>
+      </c>
+      <c r="N10" t="s">
+        <v>152</v>
+      </c>
+      <c r="O10" t="s">
+        <v>153</v>
+      </c>
+      <c r="P10" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>153</v>
+      </c>
+      <c r="R10" t="s">
+        <v>158</v>
+      </c>
+      <c r="S10" t="s">
+        <v>168</v>
+      </c>
+      <c r="T10" t="s">
+        <v>182</v>
+      </c>
+      <c r="U10" t="s">
+        <v>202</v>
+      </c>
+      <c r="V10" t="s">
+        <v>215</v>
+      </c>
+      <c r="W10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L11" t="s">
+        <v>131</v>
+      </c>
+      <c r="M11" t="s">
+        <v>141</v>
+      </c>
+      <c r="N11" t="s">
+        <v>152</v>
+      </c>
+      <c r="O11" t="s">
+        <v>153</v>
+      </c>
+      <c r="P11" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>153</v>
+      </c>
+      <c r="R11" t="s">
+        <v>159</v>
+      </c>
+      <c r="S11" t="s">
+        <v>169</v>
+      </c>
+      <c r="T11" t="s">
+        <v>183</v>
+      </c>
+      <c r="U11" t="s">
+        <v>203</v>
+      </c>
+      <c r="V11" t="s">
+        <v>212</v>
+      </c>
+      <c r="W11" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I12" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" t="s">
+        <v>127</v>
+      </c>
+      <c r="L12" t="s">
+        <v>130</v>
+      </c>
+      <c r="M12" t="s">
+        <v>142</v>
+      </c>
+      <c r="N12" t="s">
+        <v>152</v>
+      </c>
+      <c r="O12" t="s">
+        <v>153</v>
+      </c>
+      <c r="P12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>153</v>
+      </c>
+      <c r="R12" t="s">
+        <v>160</v>
+      </c>
+      <c r="S12" t="s">
+        <v>170</v>
+      </c>
+      <c r="T12" t="s">
+        <v>184</v>
+      </c>
+      <c r="U12" t="s">
+        <v>204</v>
+      </c>
+      <c r="V12" t="s">
+        <v>35</v>
+      </c>
+      <c r="W12" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" t="s">
+        <v>66</v>
+      </c>
+      <c r="H13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" t="s">
+        <v>98</v>
+      </c>
+      <c r="J13" t="s">
+        <v>115</v>
+      </c>
+      <c r="K13" t="s">
+        <v>127</v>
+      </c>
+      <c r="L13" t="s">
+        <v>130</v>
+      </c>
+      <c r="M13" t="s">
+        <v>142</v>
+      </c>
+      <c r="N13" t="s">
+        <v>152</v>
+      </c>
+      <c r="O13" t="s">
+        <v>153</v>
+      </c>
+      <c r="P13" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>153</v>
+      </c>
+      <c r="R13" t="s">
+        <v>160</v>
+      </c>
+      <c r="S13" t="s">
+        <v>170</v>
+      </c>
+      <c r="T13" t="s">
+        <v>185</v>
+      </c>
+      <c r="U13" t="s">
+        <v>204</v>
+      </c>
+      <c r="V13" t="s">
+        <v>216</v>
+      </c>
+      <c r="W13" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" t="s">
+        <v>108</v>
+      </c>
+      <c r="L14" t="s">
+        <v>131</v>
+      </c>
+      <c r="M14" t="s">
+        <v>143</v>
+      </c>
+      <c r="N14" t="s">
+        <v>152</v>
+      </c>
+      <c r="O14" t="s">
+        <v>153</v>
+      </c>
+      <c r="P14" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>153</v>
+      </c>
+      <c r="R14" t="s">
+        <v>157</v>
+      </c>
+      <c r="S14" t="s">
+        <v>46</v>
+      </c>
+      <c r="T14" t="s">
+        <v>186</v>
+      </c>
+      <c r="U14" t="s">
+        <v>203</v>
+      </c>
+      <c r="V14" t="s">
+        <v>217</v>
+      </c>
+      <c r="W14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" t="s">
+        <v>112</v>
+      </c>
+      <c r="L15" t="s">
+        <v>130</v>
+      </c>
+      <c r="M15" t="s">
+        <v>144</v>
+      </c>
+      <c r="N15" t="s">
+        <v>152</v>
+      </c>
+      <c r="O15" t="s">
+        <v>153</v>
+      </c>
+      <c r="P15" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>153</v>
+      </c>
+      <c r="R15" t="s">
+        <v>155</v>
+      </c>
+      <c r="S15" t="s">
+        <v>171</v>
+      </c>
+      <c r="T15" t="s">
+        <v>187</v>
+      </c>
+      <c r="U15" t="s">
+        <v>171</v>
+      </c>
+      <c r="V15" t="s">
+        <v>34</v>
+      </c>
+      <c r="W15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L16" t="s">
+        <v>130</v>
+      </c>
+      <c r="M16" t="s">
+        <v>145</v>
+      </c>
+      <c r="N16" t="s">
+        <v>152</v>
+      </c>
+      <c r="O16" t="s">
+        <v>153</v>
+      </c>
+      <c r="P16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>153</v>
+      </c>
+      <c r="R16" t="s">
+        <v>161</v>
+      </c>
+      <c r="S16" t="s">
+        <v>172</v>
+      </c>
+      <c r="T16" t="s">
+        <v>188</v>
+      </c>
+      <c r="U16" t="s">
+        <v>204</v>
+      </c>
+      <c r="V16" t="s">
+        <v>218</v>
+      </c>
+      <c r="W16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="G3" t="s">
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17" t="s">
+        <v>102</v>
+      </c>
+      <c r="J17" t="s">
+        <v>108</v>
+      </c>
+      <c r="K17" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" t="s">
+        <v>130</v>
+      </c>
+      <c r="M17" t="s">
+        <v>138</v>
+      </c>
+      <c r="N17" t="s">
+        <v>152</v>
+      </c>
+      <c r="O17" t="s">
+        <v>153</v>
+      </c>
+      <c r="P17" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>153</v>
+      </c>
+      <c r="R17" t="s">
+        <v>155</v>
+      </c>
+      <c r="S17" t="s">
+        <v>173</v>
+      </c>
+      <c r="T17" t="s">
+        <v>189</v>
+      </c>
+      <c r="U17" t="s">
+        <v>55</v>
+      </c>
+      <c r="V17" t="s">
+        <v>219</v>
+      </c>
+      <c r="W17" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" t="s">
+        <v>79</v>
+      </c>
+      <c r="I18" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" t="s">
+        <v>108</v>
+      </c>
+      <c r="L18" t="s">
+        <v>130</v>
+      </c>
+      <c r="M18" t="s">
+        <v>144</v>
+      </c>
+      <c r="N18" t="s">
+        <v>152</v>
+      </c>
+      <c r="O18" t="s">
+        <v>153</v>
+      </c>
+      <c r="P18" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>153</v>
+      </c>
+      <c r="R18" t="s">
+        <v>155</v>
+      </c>
+      <c r="S18" t="s">
+        <v>173</v>
+      </c>
+      <c r="T18" t="s">
+        <v>190</v>
+      </c>
+      <c r="U18" t="s">
+        <v>55</v>
+      </c>
+      <c r="V18" t="s">
+        <v>217</v>
+      </c>
+      <c r="W18" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
         <v>31</v>
       </c>
-      <c r="H3" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" t="s">
+        <v>104</v>
+      </c>
+      <c r="J19" t="s">
+        <v>108</v>
+      </c>
+      <c r="K19" t="s">
+        <v>129</v>
+      </c>
+      <c r="L19" t="s">
+        <v>130</v>
+      </c>
+      <c r="M19" t="s">
+        <v>146</v>
+      </c>
+      <c r="N19" t="s">
+        <v>152</v>
+      </c>
+      <c r="O19" t="s">
+        <v>153</v>
+      </c>
+      <c r="P19" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>153</v>
+      </c>
+      <c r="R19" t="s">
+        <v>158</v>
+      </c>
+      <c r="S19" t="s">
+        <v>174</v>
+      </c>
+      <c r="T19" t="s">
+        <v>191</v>
+      </c>
+      <c r="U19" t="s">
+        <v>205</v>
+      </c>
+      <c r="V19" t="s">
+        <v>220</v>
+      </c>
+      <c r="W19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" t="s">
+        <v>105</v>
+      </c>
+      <c r="J20" t="s">
+        <v>116</v>
+      </c>
+      <c r="K20" t="s">
+        <v>112</v>
+      </c>
+      <c r="L20" t="s">
+        <v>130</v>
+      </c>
+      <c r="M20" t="s">
+        <v>147</v>
+      </c>
+      <c r="N20" t="s">
+        <v>152</v>
+      </c>
+      <c r="O20" t="s">
+        <v>153</v>
+      </c>
+      <c r="P20" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>153</v>
+      </c>
+      <c r="R20" t="s">
+        <v>155</v>
+      </c>
+      <c r="S20" t="s">
+        <v>175</v>
+      </c>
+      <c r="T20" t="s">
+        <v>192</v>
+      </c>
+      <c r="U20" t="s">
+        <v>206</v>
+      </c>
+      <c r="V20" t="s">
+        <v>33</v>
+      </c>
+      <c r="W20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="s">
+        <v>36</v>
+      </c>
+      <c r="E21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" t="s">
+        <v>106</v>
+      </c>
+      <c r="J21" t="s">
+        <v>117</v>
+      </c>
+      <c r="K21" t="s">
+        <v>108</v>
+      </c>
+      <c r="L21" t="s">
+        <v>130</v>
+      </c>
+      <c r="M21" t="s">
+        <v>148</v>
+      </c>
+      <c r="N21" t="s">
+        <v>152</v>
+      </c>
+      <c r="O21" t="s">
+        <v>153</v>
+      </c>
+      <c r="P21" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>153</v>
+      </c>
+      <c r="R21" t="s">
+        <v>155</v>
+      </c>
+      <c r="S21" t="s">
+        <v>52</v>
+      </c>
+      <c r="T21" t="s">
+        <v>193</v>
+      </c>
+      <c r="U21" t="s">
+        <v>55</v>
+      </c>
+      <c r="V21" t="s">
+        <v>33</v>
+      </c>
+      <c r="W21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" t="s">
+        <v>84</v>
+      </c>
+      <c r="I22" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" t="s">
+        <v>108</v>
+      </c>
+      <c r="L22" t="s">
+        <v>131</v>
+      </c>
+      <c r="M22" t="s">
+        <v>149</v>
+      </c>
+      <c r="N22" t="s">
+        <v>152</v>
+      </c>
+      <c r="O22" t="s">
+        <v>153</v>
+      </c>
+      <c r="P22" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>153</v>
+      </c>
+      <c r="R22" t="s">
+        <v>162</v>
+      </c>
+      <c r="S22" t="s">
+        <v>53</v>
+      </c>
+      <c r="T22" t="s">
+        <v>194</v>
+      </c>
+      <c r="U22" t="s">
+        <v>53</v>
+      </c>
+      <c r="V22" t="s">
+        <v>34</v>
+      </c>
+      <c r="W22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
         <v>32</v>
       </c>
-      <c r="J3" t="s">
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" t="s">
+        <v>119</v>
+      </c>
+      <c r="K23" t="s">
+        <v>111</v>
+      </c>
+      <c r="L23" t="s">
+        <v>131</v>
+      </c>
+      <c r="M23" t="s">
+        <v>150</v>
+      </c>
+      <c r="N23" t="s">
+        <v>152</v>
+      </c>
+      <c r="O23" t="s">
+        <v>153</v>
+      </c>
+      <c r="P23" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>153</v>
+      </c>
+      <c r="R23" t="s">
+        <v>162</v>
+      </c>
+      <c r="S23" t="s">
+        <v>176</v>
+      </c>
+      <c r="T23" t="s">
+        <v>195</v>
+      </c>
+      <c r="U23" t="s">
+        <v>207</v>
+      </c>
+      <c r="V23" t="s">
+        <v>217</v>
+      </c>
+      <c r="W23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" t="s">
         <v>35</v>
       </c>
-      <c r="K3" t="s">
+      <c r="D24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" t="s">
+        <v>64</v>
+      </c>
+      <c r="I24" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" t="s">
+        <v>120</v>
+      </c>
+      <c r="K24" t="s">
+        <v>119</v>
+      </c>
+      <c r="L24" t="s">
+        <v>131</v>
+      </c>
+      <c r="M24" t="s">
+        <v>150</v>
+      </c>
+      <c r="N24" t="s">
+        <v>152</v>
+      </c>
+      <c r="O24" t="s">
+        <v>153</v>
+      </c>
+      <c r="P24" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>153</v>
+      </c>
+      <c r="R24" t="s">
+        <v>162</v>
+      </c>
+      <c r="S24" t="s">
+        <v>176</v>
+      </c>
+      <c r="T24" t="s">
+        <v>196</v>
+      </c>
+      <c r="U24" t="s">
+        <v>176</v>
+      </c>
+      <c r="V24" t="s">
+        <v>33</v>
+      </c>
+      <c r="W24" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" t="s">
+        <v>86</v>
+      </c>
+      <c r="I25" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" t="s">
+        <v>108</v>
+      </c>
+      <c r="K25" t="s">
+        <v>108</v>
+      </c>
+      <c r="L25" t="s">
+        <v>130</v>
+      </c>
+      <c r="M25" t="s">
+        <v>151</v>
+      </c>
+      <c r="N25" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" t="s">
+        <v>153</v>
+      </c>
+      <c r="P25" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" t="s">
+        <v>163</v>
+      </c>
+      <c r="S25" t="s">
+        <v>55</v>
+      </c>
+      <c r="T25" t="s">
+        <v>197</v>
+      </c>
+      <c r="U25" t="s">
+        <v>55</v>
+      </c>
+      <c r="V25" t="s">
         <v>34</v>
       </c>
-      <c r="L3" t="s">
-        <v>37</v>
-      </c>
-      <c r="M3" t="s">
-        <v>38</v>
-      </c>
-      <c r="N3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" t="s">
-        <v>41</v>
-      </c>
-      <c r="S3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T3" t="s">
-        <v>44</v>
-      </c>
-      <c r="U3" t="s">
-        <v>42</v>
-      </c>
-      <c r="V3" t="s">
-        <v>47</v>
-      </c>
-      <c r="W3" t="s">
-        <v>49</v>
+      <c r="W25" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
